--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -603,7 +603,7 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -849,9 +849,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.version</t>
@@ -5269,7 +5266,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>268</v>
+        <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5340,7 +5337,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>221</v>
@@ -5454,7 +5451,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>228</v>
@@ -5497,10 +5494,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>81</v>
+        <v>270</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5568,7 +5565,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>234</v>
@@ -5682,7 +5679,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>240</v>
@@ -5798,7 +5795,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>249</v>
@@ -5914,14 +5911,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5943,13 +5940,13 @@
         <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5975,11 +5972,11 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5997,7 +5994,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6012,28 +6009,28 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6052,19 +6049,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6113,7 +6110,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6128,28 +6125,28 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6168,19 +6165,19 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6229,7 +6226,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6244,28 +6241,28 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6284,19 +6281,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6345,7 +6342,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6360,28 +6357,28 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>318</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6400,19 +6397,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6461,7 +6458,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6479,25 +6476,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>328</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6516,19 +6513,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6577,7 +6574,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6592,28 +6589,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6632,19 +6629,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6693,7 +6690,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6708,24 +6705,24 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6748,19 +6745,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6809,7 +6806,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6827,10 +6824,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6838,14 +6835,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6864,19 +6861,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6925,7 +6922,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6943,10 +6940,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6954,10 +6951,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6980,16 +6977,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7039,7 +7036,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7060,7 +7057,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7068,14 +7065,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7094,19 +7091,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7155,7 +7152,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7173,10 +7170,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7184,10 +7181,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7296,10 +7293,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7410,14 +7407,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7439,10 +7436,10 @@
         <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>139</v>
@@ -7497,7 +7494,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7526,10 +7523,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7555,16 +7552,16 @@
         <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7613,7 +7610,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7634,7 +7631,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7642,10 +7639,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7668,13 +7665,13 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="M53" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7725,7 +7722,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>90</v>
@@ -7746,7 +7743,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7754,14 +7751,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7783,16 +7780,16 @@
         <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7841,7 +7838,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7859,10 +7856,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7870,10 +7867,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7899,13 +7896,13 @@
         <v>181</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7935,7 +7932,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -7953,7 +7950,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7971,10 +7968,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7982,10 +7979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8008,19 +8005,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8069,7 +8066,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8087,10 +8084,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -272,7 +272,7 @@
     <t>内視鏡を使用して実施された検査、治療に関する診断レポート。</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t>製品またはシステムが管理する、施設内で診断レポートを一意に識別するためのID。</t>
   </si>
   <si>
-    <t>通常、診断サービスプロバイダの情報システム（フィラーID）によって割り当てられる。</t>
+    <t>通常、診断サービスを実施した施設の情報システム（実施者ID、HL7 v2 の filler ID）によって割り当てられる。</t>
   </si>
   <si>
     <t>発生源の検査室からこのレポートについてクエリを作成するとき、およびFHIRコンテキスト外のレポートにリンクするときに使用する識別子を知る必要がある。</t>
@@ -830,6 +830,15 @@
     <t>JP_DiagnosticReportCategory_VSの中から「LP7796-8」（Endoscopy（内視鏡））を指定する。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP7796-8"/&gt;
+    &lt;display value="Endoscopy（内視鏡）"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
@@ -855,9 +864,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.code</t>
-  </si>
-  <si>
-    <t>LP7796-8</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.display</t>
@@ -4587,7 +4593,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4606,7 +4612,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4653,7 +4659,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>192</v>
@@ -4765,7 +4771,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>198</v>
@@ -4879,7 +4885,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>203</v>
@@ -4995,7 +5001,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>212</v>
@@ -5107,7 +5113,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>213</v>
@@ -5221,7 +5227,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>214</v>
@@ -5337,7 +5343,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>221</v>
@@ -5451,7 +5457,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>228</v>
@@ -5497,7 +5503,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
